--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 10,41</t>
+          <t>-13,11; 10,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 7,08</t>
+          <t>-14,06; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 4,54</t>
+          <t>-16,38; 3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -1,09</t>
+          <t>-13,57; -1,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 35,57</t>
+          <t>-32,77; 32,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 18,61</t>
+          <t>-30,21; 22,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 14,42</t>
+          <t>-38,93; 11,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -1,17</t>
+          <t>-13,84; -1,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 6,84</t>
+          <t>-10,42; 5,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 11,23</t>
+          <t>-6,62; 9,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 11,49</t>
+          <t>-4,61; 11,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,89</t>
+          <t>-1,38; 6,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 19,45</t>
+          <t>-24,91; 16,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 28,12</t>
+          <t>-13,58; 25,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 36,01</t>
+          <t>-11,59; 39,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,76</t>
+          <t>-1,42; 7,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 11,27</t>
+          <t>-13,8; 10,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 12,72</t>
+          <t>-9,72; 13,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 7,96</t>
+          <t>-11,58; 8,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,8</t>
+          <t>-5,56; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 26,14</t>
+          <t>-24,95; 23,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 28,86</t>
+          <t>-18,07; 31,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 19,46</t>
+          <t>-22,74; 21,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,09</t>
+          <t>-5,66; 3,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 2,57</t>
+          <t>-15,18; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 2,71</t>
+          <t>-18,55; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 15,92</t>
+          <t>-4,84; 15,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,29</t>
+          <t>-2,4; 4,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 5,67</t>
+          <t>-28,44; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 5,21</t>
+          <t>-29,45; 3,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 36,58</t>
+          <t>-9,08; 37,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,63</t>
+          <t>-2,51; 4,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,74</t>
+          <t>-8,11; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,66</t>
+          <t>-6,86; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,87</t>
+          <t>-3,21; 6,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,48</t>
+          <t>-1,85; 2,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 4,4</t>
+          <t>-17,91; 4,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 7,99</t>
+          <t>-13,63; 6,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 14,84</t>
+          <t>-7,5; 16,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,64</t>
+          <t>-1,91; 2,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 10,09</t>
+          <t>-13,75; 9,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 8,2</t>
+          <t>-13,24; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 3,55</t>
+          <t>-16,73; 3,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; -1,31</t>
+          <t>-13,55; -1,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 32,45</t>
+          <t>-33,55; 32,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 22,97</t>
+          <t>-27,7; 21,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 11,66</t>
+          <t>-39,04; 12,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -1,4</t>
+          <t>-13,93; -1,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 5,57</t>
+          <t>-9,66; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 9,98</t>
+          <t>-6,27; 11,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 11,95</t>
+          <t>-4,72; 11,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,73</t>
+          <t>-1,28; 7,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 16,77</t>
+          <t>-23,17; 18,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 25,38</t>
+          <t>-12,87; 28,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 39,17</t>
+          <t>-12,45; 38,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,42</t>
+          <t>-1,33; 7,8</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 10,25</t>
+          <t>-13,5; 11,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 13,64</t>
+          <t>-9,46; 13,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 8,37</t>
+          <t>-11,35; 8,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,99</t>
+          <t>-5,07; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 23,6</t>
+          <t>-24,8; 27,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 31,1</t>
+          <t>-17,09; 30,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 21,29</t>
+          <t>-22,87; 21,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,18</t>
+          <t>-5,25; 3,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 3,2</t>
+          <t>-15,68; 2,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 1,95</t>
+          <t>-18,62; 2,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 15,95</t>
+          <t>-4,89; 16,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,4</t>
+          <t>-2,27; 4,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 8,22</t>
+          <t>-29,06; 7,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 3,78</t>
+          <t>-29,31; 4,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 37,12</t>
+          <t>-8,99; 38,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,75</t>
+          <t>-2,36; 5,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,82</t>
+          <t>-7,75; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,27</t>
+          <t>-6,44; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,31</t>
+          <t>-3,27; 6,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,37</t>
+          <t>-1,76; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 4,36</t>
+          <t>-17,4; 4,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,96</t>
+          <t>-12,96; 7,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,33</t>
+          <t>-7,5; 16,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,53</t>
+          <t>-1,84; 2,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,29%</t>
+          <t>-5,74%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 9,89</t>
+          <t>-13,04; 10,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 8,19</t>
+          <t>-14,68; 7,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 3,74</t>
+          <t>-16,57; 4,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -1,18</t>
+          <t>-12,16; -0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 32,49</t>
+          <t>-31,1; 35,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 21,89</t>
+          <t>-30,94; 18,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 12,43</t>
+          <t>-38,54; 14,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -1,37</t>
+          <t>-12,31; -0,89</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 5,95</t>
+          <t>-9,56; 6,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 11,25</t>
+          <t>-6,1; 11,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 11,71</t>
+          <t>-4,99; 11,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 7,02</t>
+          <t>-2,48; 5,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 18,74</t>
+          <t>-23,33; 19,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 28,08</t>
+          <t>-12,96; 28,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 38,8</t>
+          <t>-12,69; 36,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,8</t>
+          <t>-2,61; 6,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,8%</t>
+          <t>-0,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 11,66</t>
+          <t>-13,14; 11,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 13,0</t>
+          <t>-9,89; 12,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 8,51</t>
+          <t>-10,99; 7,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,44</t>
+          <t>-4,49; 4,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 27,67</t>
+          <t>-24,0; 26,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 30,94</t>
+          <t>-17,78; 28,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 21,12</t>
+          <t>-22,42; 19,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,73</t>
+          <t>-4,66; 4,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 2,91</t>
+          <t>-16,15; 2,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 2,57</t>
+          <t>-18,54; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 16,18</t>
+          <t>-5,88; 15,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,65</t>
+          <t>-2,15; 4,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 7,04</t>
+          <t>-29,51; 5,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 4,34</t>
+          <t>-29,61; 5,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 38,78</t>
+          <t>-10,95; 36,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,02</t>
+          <t>-2,24; 4,8</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,86</t>
+          <t>-7,88; 1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,53</t>
+          <t>-6,47; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,24</t>
+          <t>-3,13; 5,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,34</t>
+          <t>-2,24; 2,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,67</t>
+          <t>-17,38; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,64</t>
+          <t>-12,77; 7,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,02</t>
+          <t>-7,61; 14,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,49</t>
+          <t>-2,34; 2,38</t>
         </is>
       </c>
     </row>
